--- a/VIRT.xlsx
+++ b/VIRT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F10DACAE-2CEB-439A-B273-71979682B2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82CBBF37-A79C-4DC5-91DC-C5A4AFD9BA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{F2317BC5-DDE7-4B11-8968-E77385A88B35}"/>
+    <workbookView xWindow="225" yWindow="3120" windowWidth="38175" windowHeight="15240" xr2:uid="{F2317BC5-DDE7-4B11-8968-E77385A88B35}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -2027,7 +2027,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="6">
-        <v>34.51</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H4" s="7">
         <f>+H2*H3</f>
-        <v>5275.3449914199991</v>
+        <v>7933.6541597999994</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="H7" s="7">
         <f>+H4-H5+H6</f>
-        <v>6518.1689914199997</v>
+        <v>9176.478159799999</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -30128,7 +30128,7 @@
       <c r="I3" s="33"/>
       <c r="J3" s="36">
         <f>+Main!H2</f>
-        <v>34.51</v>
+        <v>51.9</v>
       </c>
       <c r="K3" s="33"/>
       <c r="L3" s="33" t="s">
@@ -30138,7 +30138,7 @@
       <c r="N3" s="33"/>
       <c r="O3" s="36">
         <f>+J3</f>
-        <v>34.51</v>
+        <v>51.9</v>
       </c>
       <c r="P3" s="33"/>
       <c r="Q3" s="33"/>
@@ -30178,7 +30178,7 @@
       <c r="D4" s="33"/>
       <c r="E4" s="37">
         <f ca="1">+TODAY()</f>
-        <v>45937</v>
+        <v>46169</v>
       </c>
       <c r="F4" s="33"/>
       <c r="G4" s="33" t="s">
@@ -30188,7 +30188,7 @@
       <c r="I4" s="33"/>
       <c r="J4" s="38">
         <f ca="1">V62</f>
-        <v>59.115824280154861</v>
+        <v>58.86333931894854</v>
       </c>
       <c r="K4" s="33"/>
       <c r="L4" s="33" t="s">
@@ -30247,7 +30247,7 @@
       <c r="I5" s="33"/>
       <c r="J5" s="41">
         <f ca="1">J4/J3-1</f>
-        <v>0.71300562967704617</v>
+        <v>0.13416838764833416</v>
       </c>
       <c r="K5" s="33"/>
       <c r="L5" s="33" t="s">
@@ -33300,43 +33300,43 @@
       <c r="L52" s="67"/>
       <c r="M52" s="67">
         <f ca="1">(M51/(1+$E$18)^M53)*M53</f>
-        <v>178.19704656147593</v>
+        <v>306.68662097042375</v>
       </c>
       <c r="N52" s="67">
         <f ca="1">N51/(1+$E$18)^N53</f>
-        <v>724.89881724572967</v>
+        <v>712.90830041852553</v>
       </c>
       <c r="O52" s="67">
         <f t="shared" ref="O52:U52" ca="1" si="15">O51/(1+$E$18)^O53</f>
-        <v>688.04563870633228</v>
+        <v>676.66470855094997</v>
       </c>
       <c r="P52" s="67">
         <f t="shared" ca="1" si="15"/>
-        <v>653.04502429604145</v>
+        <v>642.24303763741329</v>
       </c>
       <c r="Q52" s="67">
         <f t="shared" ca="1" si="15"/>
-        <v>619.80470202489641</v>
+        <v>609.55254195454734</v>
       </c>
       <c r="R52" s="67">
         <f t="shared" ca="1" si="15"/>
-        <v>588.23696065382228</v>
+        <v>578.5069610907077</v>
       </c>
       <c r="S52" s="67">
         <f t="shared" ca="1" si="15"/>
-        <v>558.25842572552176</v>
+        <v>549.02429968152592</v>
       </c>
       <c r="T52" s="67">
         <f t="shared" ca="1" si="15"/>
-        <v>529.78984653315365</v>
+        <v>521.02661790233026</v>
       </c>
       <c r="U52" s="67">
         <f t="shared" ca="1" si="15"/>
-        <v>502.7558934952043</v>
+        <v>494.43983219462854</v>
       </c>
       <c r="V52" s="68">
         <f ca="1">V51/(1+$E$18)^V53</f>
-        <v>474.26657797956972</v>
+        <v>466.42175709070227</v>
       </c>
       <c r="W52" s="33"/>
       <c r="X52" s="33"/>
@@ -33377,43 +33377,43 @@
       <c r="L53" s="33"/>
       <c r="M53" s="95">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>0.23333333333333334</v>
+        <v>0.40833333333333333</v>
       </c>
       <c r="N53" s="95">
         <f ca="1">M53+1</f>
-        <v>1.2333333333333334</v>
+        <v>1.4083333333333332</v>
       </c>
       <c r="O53" s="95">
         <f ca="1">N53+1</f>
-        <v>2.2333333333333334</v>
+        <v>2.4083333333333332</v>
       </c>
       <c r="P53" s="95">
         <f t="shared" ref="P53:V53" ca="1" si="16">O53+1</f>
-        <v>3.2333333333333334</v>
+        <v>3.4083333333333332</v>
       </c>
       <c r="Q53" s="95">
         <f t="shared" ca="1" si="16"/>
-        <v>4.2333333333333334</v>
+        <v>4.4083333333333332</v>
       </c>
       <c r="R53" s="95">
         <f t="shared" ca="1" si="16"/>
-        <v>5.2333333333333334</v>
+        <v>5.4083333333333332</v>
       </c>
       <c r="S53" s="95">
         <f t="shared" ca="1" si="16"/>
-        <v>6.2333333333333334</v>
+        <v>6.4083333333333332</v>
       </c>
       <c r="T53" s="95">
         <f t="shared" ca="1" si="16"/>
-        <v>7.2333333333333334</v>
+        <v>7.4083333333333332</v>
       </c>
       <c r="U53" s="95">
         <f t="shared" ca="1" si="16"/>
-        <v>8.2333333333333343</v>
+        <v>8.4083333333333332</v>
       </c>
       <c r="V53" s="95">
         <f t="shared" ca="1" si="16"/>
-        <v>9.2333333333333343</v>
+        <v>9.4083333333333332</v>
       </c>
       <c r="W53" s="33"/>
       <c r="X53" s="33"/>
@@ -33463,7 +33463,7 @@
       <c r="U54" s="33"/>
       <c r="V54" s="48">
         <f ca="1">SUM(M52:V52)</f>
-        <v>5517.2989332217467</v>
+        <v>5557.4746774917539</v>
       </c>
       <c r="W54" s="33"/>
       <c r="X54" s="33"/>
@@ -33565,7 +33565,7 @@
       <c r="U56" s="71"/>
       <c r="V56" s="72">
         <f ca="1">V55/(1+E18)^V53</f>
-        <v>4762.2207355693199</v>
+        <v>4683.4490690881094</v>
       </c>
       <c r="W56" s="33"/>
       <c r="X56" s="33"/>
@@ -33615,7 +33615,7 @@
       <c r="U57" s="74"/>
       <c r="V57" s="75">
         <f ca="1">V54+V56</f>
-        <v>10279.519668791067</v>
+        <v>10240.923746579863</v>
       </c>
       <c r="W57" s="33"/>
       <c r="X57" s="33"/>
@@ -33765,7 +33765,7 @@
       <c r="U60" s="33"/>
       <c r="V60" s="76">
         <f ca="1">V57+V58-V59</f>
-        <v>9036.6956687910679</v>
+        <v>8998.0997465798646</v>
       </c>
       <c r="W60" s="33"/>
       <c r="X60" s="33"/>
@@ -33865,7 +33865,7 @@
       <c r="U62" s="33"/>
       <c r="V62" s="76">
         <f ca="1">V60/V61</f>
-        <v>59.115824280154861</v>
+        <v>58.86333931894854</v>
       </c>
       <c r="W62" s="33"/>
       <c r="X62" s="33"/>
@@ -34174,7 +34174,7 @@
       </c>
       <c r="C69" s="79">
         <f ca="1">+J4</f>
-        <v>59.115824280154861</v>
+        <v>58.86333931894854</v>
       </c>
       <c r="D69" s="80"/>
       <c r="E69" s="80"/>
@@ -34190,7 +34190,7 @@
       </c>
       <c r="N69" s="79">
         <f ca="1">+J4</f>
-        <v>59.115824280154861</v>
+        <v>58.86333931894854</v>
       </c>
       <c r="O69" s="80"/>
       <c r="P69" s="80"/>

--- a/VIRT.xlsx
+++ b/VIRT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82CBBF37-A79C-4DC5-91DC-C5A4AFD9BA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FE7ADF-869D-4F07-AA34-EF72EBE4B81C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3120" windowWidth="38175" windowHeight="15240" xr2:uid="{F2317BC5-DDE7-4B11-8968-E77385A88B35}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{F2317BC5-DDE7-4B11-8968-E77385A88B35}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -2027,7 +2027,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="6">
-        <v>51.9</v>
+        <v>59.96</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H4" s="7">
         <f>+H2*H3</f>
-        <v>7933.6541597999994</v>
+        <v>9165.7399503199995</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="H7" s="7">
         <f>+H4-H5+H6</f>
-        <v>9176.478159799999</v>
+        <v>10408.563950319998</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -30128,7 +30128,7 @@
       <c r="I3" s="33"/>
       <c r="J3" s="36">
         <f>+Main!H2</f>
-        <v>51.9</v>
+        <v>59.96</v>
       </c>
       <c r="K3" s="33"/>
       <c r="L3" s="33" t="s">
@@ -30138,7 +30138,7 @@
       <c r="N3" s="33"/>
       <c r="O3" s="36">
         <f>+J3</f>
-        <v>51.9</v>
+        <v>59.96</v>
       </c>
       <c r="P3" s="33"/>
       <c r="Q3" s="33"/>
@@ -30178,7 +30178,7 @@
       <c r="D4" s="33"/>
       <c r="E4" s="37">
         <f ca="1">+TODAY()</f>
-        <v>46169</v>
+        <v>46227</v>
       </c>
       <c r="F4" s="33"/>
       <c r="G4" s="33" t="s">
@@ -30188,7 +30188,7 @@
       <c r="I4" s="33"/>
       <c r="J4" s="38">
         <f ca="1">V62</f>
-        <v>58.86333931894854</v>
+        <v>58.626233023309958</v>
       </c>
       <c r="K4" s="33"/>
       <c r="L4" s="33" t="s">
@@ -30247,7 +30247,7 @@
       <c r="I5" s="33"/>
       <c r="J5" s="41">
         <f ca="1">J4/J3-1</f>
-        <v>0.13416838764833416</v>
+        <v>-2.2244279130921307E-2</v>
       </c>
       <c r="K5" s="33"/>
       <c r="L5" s="33" t="s">
@@ -33300,43 +33300,43 @@
       <c r="L52" s="67"/>
       <c r="M52" s="67">
         <f ca="1">(M51/(1+$E$18)^M53)*M53</f>
-        <v>306.68662097042375</v>
+        <v>419.23141737907974</v>
       </c>
       <c r="N52" s="67">
         <f ca="1">N51/(1+$E$18)^N53</f>
-        <v>712.90830041852553</v>
+        <v>702.23072826047292</v>
       </c>
       <c r="O52" s="67">
         <f t="shared" ref="O52:U52" ca="1" si="15">O51/(1+$E$18)^O53</f>
-        <v>676.66470855094997</v>
+        <v>666.52997418452628</v>
       </c>
       <c r="P52" s="67">
         <f t="shared" ca="1" si="15"/>
-        <v>642.24303763741329</v>
+        <v>632.62385327197046</v>
       </c>
       <c r="Q52" s="67">
         <f t="shared" ca="1" si="15"/>
-        <v>609.55254195454734</v>
+        <v>600.42297894199294</v>
       </c>
       <c r="R52" s="67">
         <f t="shared" ca="1" si="15"/>
-        <v>578.5069610907077</v>
+        <v>569.84238274682343</v>
       </c>
       <c r="S52" s="67">
         <f t="shared" ca="1" si="15"/>
-        <v>549.02429968152592</v>
+        <v>540.80129740629332</v>
       </c>
       <c r="T52" s="67">
         <f t="shared" ca="1" si="15"/>
-        <v>521.02661790233026</v>
+        <v>513.22295043815268</v>
       </c>
       <c r="U52" s="67">
         <f t="shared" ca="1" si="15"/>
-        <v>494.43983219462854</v>
+        <v>487.03436786916882</v>
       </c>
       <c r="V52" s="68">
         <f ca="1">V51/(1+$E$18)^V53</f>
-        <v>466.42175709070227</v>
+        <v>459.43593301697797</v>
       </c>
       <c r="W52" s="33"/>
       <c r="X52" s="33"/>
@@ -33377,43 +33377,43 @@
       <c r="L53" s="33"/>
       <c r="M53" s="95">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>0.40833333333333333</v>
+        <v>0.56666666666666665</v>
       </c>
       <c r="N53" s="95">
         <f ca="1">M53+1</f>
-        <v>1.4083333333333332</v>
+        <v>1.5666666666666667</v>
       </c>
       <c r="O53" s="95">
         <f ca="1">N53+1</f>
-        <v>2.4083333333333332</v>
+        <v>2.5666666666666664</v>
       </c>
       <c r="P53" s="95">
         <f t="shared" ref="P53:V53" ca="1" si="16">O53+1</f>
-        <v>3.4083333333333332</v>
+        <v>3.5666666666666664</v>
       </c>
       <c r="Q53" s="95">
         <f t="shared" ca="1" si="16"/>
-        <v>4.4083333333333332</v>
+        <v>4.5666666666666664</v>
       </c>
       <c r="R53" s="95">
         <f t="shared" ca="1" si="16"/>
-        <v>5.4083333333333332</v>
+        <v>5.5666666666666664</v>
       </c>
       <c r="S53" s="95">
         <f t="shared" ca="1" si="16"/>
-        <v>6.4083333333333332</v>
+        <v>6.5666666666666664</v>
       </c>
       <c r="T53" s="95">
         <f t="shared" ca="1" si="16"/>
-        <v>7.4083333333333332</v>
+        <v>7.5666666666666664</v>
       </c>
       <c r="U53" s="95">
         <f t="shared" ca="1" si="16"/>
-        <v>8.4083333333333332</v>
+        <v>8.5666666666666664</v>
       </c>
       <c r="V53" s="95">
         <f t="shared" ca="1" si="16"/>
-        <v>9.4083333333333332</v>
+        <v>9.5666666666666664</v>
       </c>
       <c r="W53" s="33"/>
       <c r="X53" s="33"/>
@@ -33463,7 +33463,7 @@
       <c r="U54" s="33"/>
       <c r="V54" s="48">
         <f ca="1">SUM(M52:V52)</f>
-        <v>5557.4746774917539</v>
+        <v>5591.3758835154586</v>
       </c>
       <c r="W54" s="33"/>
       <c r="X54" s="33"/>
@@ -33565,7 +33565,7 @@
       <c r="U56" s="71"/>
       <c r="V56" s="72">
         <f ca="1">V55/(1+E18)^V53</f>
-        <v>4683.4490690881094</v>
+        <v>4613.3027889081841</v>
       </c>
       <c r="W56" s="33"/>
       <c r="X56" s="33"/>
@@ -33615,7 +33615,7 @@
       <c r="U57" s="74"/>
       <c r="V57" s="75">
         <f ca="1">V54+V56</f>
-        <v>10240.923746579863</v>
+        <v>10204.678672423643</v>
       </c>
       <c r="W57" s="33"/>
       <c r="X57" s="33"/>
@@ -33765,7 +33765,7 @@
       <c r="U60" s="33"/>
       <c r="V60" s="76">
         <f ca="1">V57+V58-V59</f>
-        <v>8998.0997465798646</v>
+        <v>8961.8546724236439</v>
       </c>
       <c r="W60" s="33"/>
       <c r="X60" s="33"/>
@@ -33865,7 +33865,7 @@
       <c r="U62" s="33"/>
       <c r="V62" s="76">
         <f ca="1">V60/V61</f>
-        <v>58.86333931894854</v>
+        <v>58.626233023309958</v>
       </c>
       <c r="W62" s="33"/>
       <c r="X62" s="33"/>
@@ -34174,7 +34174,7 @@
       </c>
       <c r="C69" s="79">
         <f ca="1">+J4</f>
-        <v>58.86333931894854</v>
+        <v>58.626233023309958</v>
       </c>
       <c r="D69" s="80"/>
       <c r="E69" s="80"/>
@@ -34190,7 +34190,7 @@
       </c>
       <c r="N69" s="79">
         <f ca="1">+J4</f>
-        <v>58.86333931894854</v>
+        <v>58.626233023309958</v>
       </c>
       <c r="O69" s="80"/>
       <c r="P69" s="80"/>
